--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_2.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_2.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HSbank_branches20201013\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="30" windowWidth="20490" windowHeight="7740"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
   </bookViews>
   <sheets>
     <sheet name="表1-2募集及兑付发生额" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -32,9 +37,6 @@
   </si>
   <si>
     <t>产品品种：</t>
-  </si>
-  <si>
-    <t>单位：万元</t>
   </si>
   <si>
     <t>列编号</t>
@@ -194,6 +196,7 @@
         <b/>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产品类型</t>
@@ -222,6 +225,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>分级产品</t>
@@ -1411,6 +1415,10 @@
   </si>
   <si>
     <t>${report.enddate}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：万元</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1424,7 +1432,7 @@
     <numFmt numFmtId="178" formatCode="##0.00"/>
     <numFmt numFmtId="179" formatCode="#,##0.000000_ "/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1436,44 +1444,52 @@
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1485,11 +1501,13 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1500,7 +1518,16 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1843,7 +1870,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2006,6 +2033,33 @@
     <xf numFmtId="179" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2030,49 +2084,25 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2125,6 +2155,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2385,7 +2418,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2406,25 +2439,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24.95" customHeight="1">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
     </row>
     <row r="2" spans="1:18" s="11" customFormat="1" ht="24.95" customHeight="1">
       <c r="A2" s="2"/>
@@ -2438,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
@@ -2454,38 +2487,38 @@
         <v>2</v>
       </c>
       <c r="B3" s="12"/>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="60" t="s">
+        <v>406</v>
+      </c>
+      <c r="D3" s="61"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="62" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="63"/>
+      <c r="I3" s="60" t="s">
         <v>407</v>
       </c>
-      <c r="D3" s="72"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="73" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="74"/>
-      <c r="I3" s="71" t="s">
-        <v>408</v>
-      </c>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
       <c r="L3" s="13"/>
       <c r="O3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="71" t="s">
-        <v>409</v>
-      </c>
-      <c r="Q3" s="75"/>
+      <c r="P3" s="60" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q3" s="64"/>
     </row>
     <row r="4" spans="1:18" s="10" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
       <c r="A4" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="56" t="s">
-        <v>410</v>
-      </c>
-      <c r="C4" s="56"/>
+      <c r="B4" s="65" t="s">
+        <v>409</v>
+      </c>
+      <c r="C4" s="65"/>
       <c r="D4" s="46"/>
       <c r="E4" s="47"/>
       <c r="F4" s="48"/>
@@ -2499,193 +2532,193 @@
       <c r="N4" s="51"/>
       <c r="O4" s="51"/>
       <c r="P4" s="53"/>
-      <c r="Q4" s="53" t="s">
-        <v>6</v>
+      <c r="Q4" s="56" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="5" spans="1:18" s="10" customFormat="1" ht="13.5" customHeight="1">
       <c r="A5" s="14"/>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="66" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="66"/>
+      <c r="D5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="H5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="I5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="J5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="K5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="L5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="M5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="N5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="O5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="P5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="16" t="s">
+      <c r="Q5" s="16" t="s">
         <v>20</v>
-      </c>
-      <c r="Q5" s="16" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:18" s="11" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="C6" s="69"/>
+      <c r="D6" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="60"/>
-      <c r="D6" s="63" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="63"/>
-      <c r="P6" s="63"/>
-      <c r="Q6" s="63"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
     </row>
     <row r="7" spans="1:18" s="19" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A7" s="58"/>
-      <c r="B7" s="61"/>
-      <c r="C7" s="62"/>
+      <c r="A7" s="67"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="71"/>
       <c r="D7" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="F7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="G7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="H7" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="I7" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="J7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="18" t="s">
-        <v>32</v>
-      </c>
       <c r="K7" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="M7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="18" t="s">
+      <c r="N7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="18" t="s">
+      <c r="O7" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="18" t="s">
+      <c r="P7" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="P7" s="18" t="s">
+      <c r="Q7" s="18" t="s">
         <v>31</v>
-      </c>
-      <c r="Q7" s="18" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:18" s="21" customFormat="1" ht="15.95" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>411</v>
-      </c>
-      <c r="B8" s="68" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="69"/>
+        <v>410</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="58"/>
       <c r="D8" s="44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G8" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I8" s="44" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J8" s="44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N8" s="44" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O8" s="44" t="s">
+        <v>331</v>
+      </c>
+      <c r="P8" s="44" t="s">
         <v>332</v>
       </c>
-      <c r="P8" s="44" t="s">
+      <c r="Q8" s="55" t="s">
         <v>333</v>
-      </c>
-      <c r="Q8" s="55" t="s">
-        <v>334</v>
       </c>
       <c r="R8" s="54"/>
     </row>
     <row r="9" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>412</v>
-      </c>
-      <c r="B9" s="77" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="78"/>
+        <v>411</v>
+      </c>
+      <c r="B9" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="76"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
@@ -2703,318 +2736,318 @@
     </row>
     <row r="10" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>413</v>
-      </c>
-      <c r="B10" s="66" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="67"/>
+        <v>412</v>
+      </c>
+      <c r="B10" s="73" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="74"/>
       <c r="D10" s="44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O10" s="44" t="s">
+        <v>334</v>
+      </c>
+      <c r="P10" s="44" t="s">
         <v>335</v>
       </c>
-      <c r="P10" s="44" t="s">
+      <c r="Q10" s="55" t="s">
         <v>336</v>
-      </c>
-      <c r="Q10" s="55" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>414</v>
-      </c>
-      <c r="B11" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="67"/>
+        <v>413</v>
+      </c>
+      <c r="B11" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="74"/>
       <c r="D11" s="44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O11" s="44" t="s">
+        <v>337</v>
+      </c>
+      <c r="P11" s="44" t="s">
         <v>338</v>
       </c>
-      <c r="P11" s="44" t="s">
+      <c r="Q11" s="55" t="s">
         <v>339</v>
-      </c>
-      <c r="Q11" s="55" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>415</v>
-      </c>
-      <c r="B12" s="66" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="67"/>
+        <v>414</v>
+      </c>
+      <c r="B12" s="73" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="74"/>
       <c r="D12" s="44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O12" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="P12" s="44" t="s">
         <v>341</v>
       </c>
-      <c r="P12" s="44" t="s">
+      <c r="Q12" s="44" t="s">
         <v>342</v>
-      </c>
-      <c r="Q12" s="44" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>416</v>
-      </c>
-      <c r="B13" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="67"/>
+        <v>415</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="74"/>
       <c r="D13" s="44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M13" s="44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O13" s="44" t="s">
+        <v>343</v>
+      </c>
+      <c r="P13" s="44" t="s">
         <v>344</v>
       </c>
-      <c r="P13" s="44" t="s">
+      <c r="Q13" s="44" t="s">
         <v>345</v>
-      </c>
-      <c r="Q13" s="44" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A14" s="43" t="s">
-        <v>417</v>
-      </c>
-      <c r="B14" s="66" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="67"/>
+        <v>416</v>
+      </c>
+      <c r="B14" s="73" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="74"/>
       <c r="D14" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N14" s="44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O14" s="44" t="s">
+        <v>346</v>
+      </c>
+      <c r="P14" s="44" t="s">
         <v>347</v>
       </c>
-      <c r="P14" s="44" t="s">
+      <c r="Q14" s="44" t="s">
         <v>348</v>
-      </c>
-      <c r="Q14" s="44" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="15" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>418</v>
-      </c>
-      <c r="B15" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="67"/>
+        <v>417</v>
+      </c>
+      <c r="B15" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="74"/>
       <c r="D15" s="44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M15" s="44" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N15" s="44" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O15" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="P15" s="44" t="s">
         <v>350</v>
       </c>
-      <c r="P15" s="44" t="s">
+      <c r="Q15" s="44" t="s">
         <v>351</v>
-      </c>
-      <c r="Q15" s="44" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:18" s="26" customFormat="1" ht="15.95" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>419</v>
-      </c>
-      <c r="B16" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="65"/>
+        <v>418</v>
+      </c>
+      <c r="B16" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="78"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -3032,216 +3065,216 @@
     </row>
     <row r="17" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>420</v>
-      </c>
-      <c r="B17" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="67"/>
+        <v>419</v>
+      </c>
+      <c r="B17" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="74"/>
       <c r="D17" s="44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O17" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="P17" s="44" t="s">
         <v>353</v>
       </c>
-      <c r="P17" s="44" t="s">
+      <c r="Q17" s="44" t="s">
         <v>354</v>
-      </c>
-      <c r="Q17" s="44" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>421</v>
-      </c>
-      <c r="B18" s="66" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="67"/>
+        <v>420</v>
+      </c>
+      <c r="B18" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="74"/>
       <c r="D18" s="44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F18" s="44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H18" s="44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I18" s="44" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J18" s="44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K18" s="44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L18" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M18" s="44" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N18" s="44" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O18" s="44" t="s">
+        <v>355</v>
+      </c>
+      <c r="P18" s="44" t="s">
         <v>356</v>
       </c>
-      <c r="P18" s="44" t="s">
+      <c r="Q18" s="44" t="s">
         <v>357</v>
-      </c>
-      <c r="Q18" s="44" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>422</v>
-      </c>
-      <c r="B19" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="67"/>
+        <v>421</v>
+      </c>
+      <c r="B19" s="73" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="74"/>
       <c r="D19" s="44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H19" s="44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K19" s="44" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L19" s="44" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M19" s="44" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N19" s="44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O19" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="P19" s="44" t="s">
         <v>359</v>
       </c>
-      <c r="P19" s="44" t="s">
+      <c r="Q19" s="44" t="s">
         <v>360</v>
-      </c>
-      <c r="Q19" s="44" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>423</v>
-      </c>
-      <c r="B20" s="66" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="67"/>
+        <v>422</v>
+      </c>
+      <c r="B20" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="74"/>
       <c r="D20" s="44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H20" s="44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K20" s="44" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L20" s="44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M20" s="44" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N20" s="44" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O20" s="44" t="s">
+        <v>361</v>
+      </c>
+      <c r="P20" s="44" t="s">
         <v>362</v>
       </c>
-      <c r="P20" s="44" t="s">
+      <c r="Q20" s="44" t="s">
         <v>363</v>
-      </c>
-      <c r="Q20" s="44" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>424</v>
-      </c>
-      <c r="B21" s="77" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="78"/>
+        <v>423</v>
+      </c>
+      <c r="B21" s="75" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="76"/>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
@@ -3259,114 +3292,114 @@
     </row>
     <row r="22" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>425</v>
-      </c>
-      <c r="B22" s="66" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="67"/>
+        <v>424</v>
+      </c>
+      <c r="B22" s="73" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="74"/>
       <c r="D22" s="44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H22" s="44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K22" s="44" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L22" s="44" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M22" s="44" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N22" s="44" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O22" s="44" t="s">
+        <v>364</v>
+      </c>
+      <c r="P22" s="44" t="s">
         <v>365</v>
       </c>
-      <c r="P22" s="44" t="s">
+      <c r="Q22" s="44" t="s">
         <v>366</v>
-      </c>
-      <c r="Q22" s="44" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>426</v>
-      </c>
-      <c r="B23" s="66" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="67"/>
+        <v>425</v>
+      </c>
+      <c r="B23" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="74"/>
       <c r="D23" s="44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H23" s="44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K23" s="44" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L23" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M23" s="44" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N23" s="44" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O23" s="44" t="s">
+        <v>367</v>
+      </c>
+      <c r="P23" s="44" t="s">
         <v>368</v>
       </c>
-      <c r="P23" s="44" t="s">
+      <c r="Q23" s="44" t="s">
         <v>369</v>
-      </c>
-      <c r="Q23" s="44" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A24" s="43" t="s">
-        <v>427</v>
-      </c>
-      <c r="B24" s="79" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="80"/>
+        <v>426</v>
+      </c>
+      <c r="B24" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="81"/>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -3384,114 +3417,114 @@
     </row>
     <row r="25" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A25" s="43" t="s">
-        <v>428</v>
-      </c>
-      <c r="B25" s="81" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="76"/>
+        <v>427</v>
+      </c>
+      <c r="B25" s="82" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="79"/>
       <c r="D25" s="44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G25" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H25" s="44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I25" s="44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J25" s="44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K25" s="44" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L25" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M25" s="44" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N25" s="44" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O25" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="P25" s="44" t="s">
         <v>371</v>
       </c>
-      <c r="P25" s="44" t="s">
+      <c r="Q25" s="44" t="s">
         <v>372</v>
-      </c>
-      <c r="Q25" s="44" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
       <c r="A26" s="43" t="s">
-        <v>429</v>
-      </c>
-      <c r="B26" s="81" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="76"/>
+        <v>428</v>
+      </c>
+      <c r="B26" s="82" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="79"/>
       <c r="D26" s="44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F26" s="44" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G26" s="44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H26" s="44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I26" s="44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J26" s="44" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L26" s="44" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M26" s="44" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N26" s="44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O26" s="44" t="s">
+        <v>373</v>
+      </c>
+      <c r="P26" s="44" t="s">
         <v>374</v>
       </c>
-      <c r="P26" s="44" t="s">
+      <c r="Q26" s="44" t="s">
         <v>375</v>
-      </c>
-      <c r="Q26" s="44" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>430</v>
-      </c>
-      <c r="B27" s="79" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="80"/>
+        <v>429</v>
+      </c>
+      <c r="B27" s="80" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="81"/>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
@@ -3509,114 +3542,114 @@
     </row>
     <row r="28" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>431</v>
-      </c>
-      <c r="B28" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="76"/>
+        <v>430</v>
+      </c>
+      <c r="B28" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="79"/>
       <c r="D28" s="44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F28" s="44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G28" s="44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H28" s="44" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I28" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J28" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K28" s="44" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L28" s="44" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M28" s="44" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N28" s="44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O28" s="44" t="s">
+        <v>376</v>
+      </c>
+      <c r="P28" s="44" t="s">
         <v>377</v>
       </c>
-      <c r="P28" s="44" t="s">
+      <c r="Q28" s="44" t="s">
         <v>378</v>
-      </c>
-      <c r="Q28" s="44" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>432</v>
-      </c>
-      <c r="B29" s="82" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="83"/>
+        <v>431</v>
+      </c>
+      <c r="B29" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="84"/>
       <c r="D29" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G29" s="44" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H29" s="44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I29" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J29" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K29" s="44" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L29" s="44" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M29" s="44" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N29" s="44" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O29" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="P29" s="44" t="s">
         <v>380</v>
       </c>
-      <c r="P29" s="44" t="s">
+      <c r="Q29" s="44" t="s">
         <v>381</v>
-      </c>
-      <c r="Q29" s="44" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
       <c r="A30" s="20" t="s">
-        <v>441</v>
-      </c>
-      <c r="B30" s="76" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="76"/>
+        <v>440</v>
+      </c>
+      <c r="B30" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="79"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -3634,216 +3667,216 @@
     </row>
     <row r="31" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
       <c r="A31" s="43" t="s">
-        <v>433</v>
-      </c>
-      <c r="B31" s="76" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="76"/>
+        <v>432</v>
+      </c>
+      <c r="B31" s="79" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="79"/>
       <c r="D31" s="44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G31" s="44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H31" s="44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I31" s="44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J31" s="44" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K31" s="44" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L31" s="44" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M31" s="44" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N31" s="44" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O31" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="P31" s="44" t="s">
         <v>383</v>
       </c>
-      <c r="P31" s="44" t="s">
+      <c r="Q31" s="44" t="s">
         <v>384</v>
-      </c>
-      <c r="Q31" s="44" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
       <c r="A32" s="20" t="s">
-        <v>435</v>
-      </c>
-      <c r="B32" s="76" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="76"/>
+        <v>434</v>
+      </c>
+      <c r="B32" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="79"/>
       <c r="D32" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F32" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G32" s="44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H32" s="44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I32" s="44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J32" s="44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K32" s="44" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L32" s="44" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M32" s="44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N32" s="44" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O32" s="44" t="s">
+        <v>385</v>
+      </c>
+      <c r="P32" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="P32" s="44" t="s">
+      <c r="Q32" s="44" t="s">
         <v>387</v>
-      </c>
-      <c r="Q32" s="44" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
       <c r="A33" s="20" t="s">
-        <v>440</v>
-      </c>
-      <c r="B33" s="76" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="76"/>
+        <v>439</v>
+      </c>
+      <c r="B33" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="79"/>
       <c r="D33" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F33" s="44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G33" s="44" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H33" s="44" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I33" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J33" s="44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K33" s="44" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L33" s="44" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M33" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N33" s="44" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O33" s="44" t="s">
+        <v>388</v>
+      </c>
+      <c r="P33" s="44" t="s">
         <v>389</v>
       </c>
-      <c r="P33" s="44" t="s">
+      <c r="Q33" s="44" t="s">
         <v>390</v>
-      </c>
-      <c r="Q33" s="44" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1" thickBot="1">
       <c r="A34" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="B34" s="85" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="86"/>
+        <v>437</v>
+      </c>
+      <c r="B34" s="86" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="87"/>
       <c r="D34" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F34" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G34" s="44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H34" s="44" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I34" s="44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J34" s="44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K34" s="44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L34" s="44" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M34" s="44" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N34" s="44" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O34" s="44" t="s">
+        <v>391</v>
+      </c>
+      <c r="P34" s="44" t="s">
         <v>392</v>
       </c>
-      <c r="P34" s="44" t="s">
+      <c r="Q34" s="44" t="s">
         <v>393</v>
-      </c>
-      <c r="Q34" s="44" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1" thickTop="1">
       <c r="A35" s="20" t="s">
-        <v>439</v>
-      </c>
-      <c r="B35" s="87" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="88"/>
+        <v>438</v>
+      </c>
+      <c r="B35" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="89"/>
       <c r="D35" s="27"/>
       <c r="E35" s="28"/>
       <c r="F35" s="29"/>
@@ -3861,194 +3894,194 @@
     </row>
     <row r="36" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
       <c r="A36" s="20" t="s">
-        <v>437</v>
-      </c>
-      <c r="B36" s="81" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" s="76"/>
+        <v>436</v>
+      </c>
+      <c r="B36" s="82" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="79"/>
       <c r="D36" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F36" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G36" s="44" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H36" s="44" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I36" s="44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J36" s="44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K36" s="44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L36" s="44" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M36" s="44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N36" s="44" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O36" s="44" t="s">
+        <v>394</v>
+      </c>
+      <c r="P36" s="44" t="s">
         <v>395</v>
       </c>
-      <c r="P36" s="44" t="s">
+      <c r="Q36" s="44" t="s">
         <v>396</v>
-      </c>
-      <c r="Q36" s="44" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
       <c r="A37" s="43" t="s">
-        <v>434</v>
-      </c>
-      <c r="B37" s="89" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" s="81"/>
+        <v>433</v>
+      </c>
+      <c r="B37" s="90" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="82"/>
       <c r="D37" s="44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F37" s="44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G37" s="44" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H37" s="44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I37" s="44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J37" s="44" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K37" s="44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L37" s="44" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M37" s="44" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N37" s="44" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O37" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="P37" s="44" t="s">
         <v>398</v>
       </c>
-      <c r="P37" s="44" t="s">
+      <c r="Q37" s="44" t="s">
         <v>399</v>
-      </c>
-      <c r="Q37" s="44" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1" thickBot="1">
       <c r="A38" s="20" t="s">
-        <v>436</v>
-      </c>
-      <c r="B38" s="90" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="91"/>
+        <v>435</v>
+      </c>
+      <c r="B38" s="91" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="92"/>
       <c r="D38" s="44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F38" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G38" s="44" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H38" s="44" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I38" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J38" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K38" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L38" s="44" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M38" s="44" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N38" s="44" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O38" s="44" t="s">
+        <v>400</v>
+      </c>
+      <c r="P38" s="44" t="s">
         <v>401</v>
       </c>
-      <c r="P38" s="44" t="s">
+      <c r="Q38" s="44" t="s">
         <v>402</v>
-      </c>
-      <c r="Q38" s="44" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="11" customFormat="1" ht="48.75" customHeight="1">
-      <c r="A39" s="84" t="s">
-        <v>64</v>
-      </c>
-      <c r="B39" s="84"/>
-      <c r="C39" s="84"/>
-      <c r="D39" s="84"/>
-      <c r="E39" s="84"/>
-      <c r="F39" s="84"/>
-      <c r="G39" s="84"/>
-      <c r="H39" s="84"/>
-      <c r="I39" s="84"/>
-      <c r="J39" s="84"/>
-      <c r="K39" s="84"/>
-      <c r="L39" s="84"/>
-      <c r="M39" s="84"/>
-      <c r="N39" s="84"/>
-      <c r="O39" s="84"/>
-      <c r="P39" s="84"/>
-      <c r="Q39" s="84"/>
+      <c r="A39" s="85" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" s="85"/>
+      <c r="C39" s="85"/>
+      <c r="D39" s="85"/>
+      <c r="E39" s="85"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="85"/>
+      <c r="H39" s="85"/>
+      <c r="I39" s="85"/>
+      <c r="J39" s="85"/>
+      <c r="K39" s="85"/>
+      <c r="L39" s="85"/>
+      <c r="M39" s="85"/>
+      <c r="N39" s="85"/>
+      <c r="O39" s="85"/>
+      <c r="P39" s="85"/>
+      <c r="Q39" s="85"/>
     </row>
     <row r="40" spans="1:17" s="33" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A40" s="31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B40" s="31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C40" s="31"/>
       <c r="D40" s="31"/>
       <c r="E40" s="32"/>
       <c r="F40" s="31"/>
       <c r="G40" s="33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H40" s="34" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I40" s="34"/>
       <c r="J40" s="34"/>
@@ -4058,10 +4091,10 @@
       <c r="N40" s="37"/>
       <c r="O40" s="31"/>
       <c r="P40" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q40" s="38" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="14.25" customHeight="1">

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_2.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HSbank_branches20201013\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\ZGBS-CP\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A224CE5-FC4B-44A0-B10B-AF9AFBFEDAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表1-2募集及兑付发生额" sheetId="1" r:id="rId1"/>
@@ -235,9 +236,6 @@
     <t xml:space="preserve"> 其中：收益权转让产品</t>
   </si>
   <si>
-    <t xml:space="preserve"> 其中：货币市场基金</t>
-  </si>
-  <si>
     <t>注：1.产品品种取值范围为：01-银行非保本理财，02-信托公司资管产品，03-证券公司及其子公司资管产品，04-基金管理公司及其子公司专户，05-期货公司及其子公司资管产品，06-保险资管产品，07-金融资产投资公司资管产品，08-公募基金。通过下拉选项选择。
     2.各币种折人民币汇率使用报告期最后一个交易日外汇局公布的各币种折人民币汇率中间价。
     3.数据精度要求：至少保留2位小数。
@@ -1421,11 +1419,15 @@
     <t>单位：万元</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve"> 其中：货币市场基金或现金管理类产品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
@@ -2036,6 +2038,66 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2083,72 +2145,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
-    <cellStyle name="常规_demo-交叉报表（列标题分为2级）" xfId="2"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规_demo-交叉报表（列标题分为2级）" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2425,41 +2427,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr defaultRowHeight="20.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.399999999999999"/>
   <cols>
     <col min="1" max="1" width="11" style="39" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="42" customWidth="1"/>
-    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.625" style="41" customWidth="1"/>
-    <col min="6" max="17" width="12.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="42" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="41" customWidth="1"/>
+    <col min="6" max="17" width="12.6640625" style="1" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24.95" customHeight="1">
-      <c r="A1" s="59" t="s">
+    <row r="1" spans="1:18" ht="24.9" customHeight="1">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
     </row>
-    <row r="2" spans="1:18" s="11" customFormat="1" ht="24.95" customHeight="1">
+    <row r="2" spans="1:18" s="11" customFormat="1" ht="24.9" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2471,7 +2473,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
@@ -2482,43 +2484,43 @@
       <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
     </row>
-    <row r="3" spans="1:18" s="11" customFormat="1" ht="24.95" customHeight="1">
+    <row r="3" spans="1:18" s="11" customFormat="1" ht="24.9" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="12"/>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="80" t="s">
+        <v>405</v>
+      </c>
+      <c r="D3" s="81"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="83"/>
+      <c r="I3" s="80" t="s">
         <v>406</v>
       </c>
-      <c r="D3" s="61"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="62" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="63"/>
-      <c r="I3" s="60" t="s">
-        <v>407</v>
-      </c>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
       <c r="L3" s="13"/>
       <c r="O3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="60" t="s">
-        <v>408</v>
-      </c>
-      <c r="Q3" s="64"/>
+      <c r="P3" s="80" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q3" s="84"/>
     </row>
-    <row r="4" spans="1:18" s="10" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
+    <row r="4" spans="1:18" s="10" customFormat="1" ht="24.9" customHeight="1" thickBot="1">
       <c r="A4" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="65" t="s">
-        <v>409</v>
-      </c>
-      <c r="C4" s="65"/>
+      <c r="B4" s="85" t="s">
+        <v>408</v>
+      </c>
+      <c r="C4" s="85"/>
       <c r="D4" s="46"/>
       <c r="E4" s="47"/>
       <c r="F4" s="48"/>
@@ -2533,15 +2535,15 @@
       <c r="O4" s="51"/>
       <c r="P4" s="53"/>
       <c r="Q4" s="56" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:18" s="10" customFormat="1" ht="13.5" customHeight="1">
       <c r="A5" s="14"/>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="66"/>
+      <c r="C5" s="86"/>
       <c r="D5" s="15" t="s">
         <v>7</v>
       </c>
@@ -2585,37 +2587,37 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="11" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A6" s="67" t="s">
+    <row r="6" spans="1:18" s="11" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A6" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="72" t="s">
+      <c r="C6" s="89"/>
+      <c r="D6" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72" t="s">
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="72"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
+      <c r="L6" s="92"/>
+      <c r="M6" s="92"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="92"/>
+      <c r="Q6" s="92"/>
     </row>
     <row r="7" spans="1:18" s="19" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A7" s="67"/>
-      <c r="B7" s="70"/>
-      <c r="C7" s="71"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="91"/>
       <c r="D7" s="17" t="s">
         <v>25</v>
       </c>
@@ -2659,66 +2661,66 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="21" customFormat="1" ht="15.95" customHeight="1">
+    <row r="8" spans="1:18" s="21" customFormat="1" ht="15.9" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>410</v>
-      </c>
-      <c r="B8" s="57" t="s">
+        <v>409</v>
+      </c>
+      <c r="B8" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="58"/>
+      <c r="C8" s="78"/>
       <c r="D8" s="44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G8" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I8" s="44" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J8" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N8" s="44" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O8" s="44" t="s">
+        <v>330</v>
+      </c>
+      <c r="P8" s="44" t="s">
         <v>331</v>
       </c>
-      <c r="P8" s="44" t="s">
+      <c r="Q8" s="55" t="s">
         <v>332</v>
-      </c>
-      <c r="Q8" s="55" t="s">
-        <v>333</v>
       </c>
       <c r="R8" s="54"/>
     </row>
-    <row r="9" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
+    <row r="9" spans="1:18" s="24" customFormat="1" ht="15.9" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>411</v>
-      </c>
-      <c r="B9" s="75" t="s">
+        <v>410</v>
+      </c>
+      <c r="B9" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="76"/>
+      <c r="C9" s="68"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
@@ -2734,320 +2736,320 @@
       <c r="P9" s="23"/>
       <c r="Q9" s="23"/>
     </row>
-    <row r="10" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
+    <row r="10" spans="1:18" s="24" customFormat="1" ht="15.9" customHeight="1">
       <c r="A10" s="43" t="s">
+        <v>411</v>
+      </c>
+      <c r="B10" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="70"/>
+      <c r="D10" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="I10" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="J10" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="K10" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="L10" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="M10" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="N10" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="O10" s="44" t="s">
+        <v>333</v>
+      </c>
+      <c r="P10" s="44" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q10" s="55" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A11" s="43" t="s">
         <v>412</v>
       </c>
-      <c r="B10" s="73" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="44" t="s">
+      <c r="B11" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="70"/>
+      <c r="D11" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E11" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F11" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="G10" s="44" t="s">
+      <c r="G11" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H11" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="I11" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="J10" s="44" t="s">
+      <c r="J11" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="K10" s="44" t="s">
+      <c r="K11" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="L10" s="44" t="s">
+      <c r="L11" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="M10" s="44" t="s">
+      <c r="M11" s="44" t="s">
         <v>284</v>
       </c>
-      <c r="N10" s="44" t="s">
+      <c r="N11" s="44" t="s">
         <v>308</v>
       </c>
-      <c r="O10" s="44" t="s">
-        <v>334</v>
-      </c>
-      <c r="P10" s="44" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q10" s="55" t="s">
+      <c r="O11" s="44" t="s">
         <v>336</v>
       </c>
+      <c r="P11" s="44" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q11" s="55" t="s">
+        <v>338</v>
+      </c>
     </row>
-    <row r="11" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A11" s="43" t="s">
+    <row r="12" spans="1:18" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A12" s="43" t="s">
         <v>413</v>
       </c>
-      <c r="B11" s="73" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="44" t="s">
+      <c r="B12" s="69" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="70"/>
+      <c r="D12" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E12" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="44" t="s">
+      <c r="F12" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="G11" s="44" t="s">
+      <c r="G12" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H12" s="44" t="s">
         <v>165</v>
       </c>
-      <c r="I11" s="44" t="s">
+      <c r="I12" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="J11" s="44" t="s">
+      <c r="J12" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="K11" s="44" t="s">
+      <c r="K12" s="44" t="s">
         <v>237</v>
       </c>
-      <c r="L11" s="44" t="s">
+      <c r="L12" s="44" t="s">
         <v>261</v>
       </c>
-      <c r="M11" s="44" t="s">
+      <c r="M12" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="N11" s="44" t="s">
+      <c r="N12" s="44" t="s">
         <v>309</v>
       </c>
-      <c r="O11" s="44" t="s">
-        <v>337</v>
-      </c>
-      <c r="P11" s="44" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q11" s="55" t="s">
+      <c r="O12" s="44" t="s">
         <v>339</v>
       </c>
+      <c r="P12" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q12" s="44" t="s">
+        <v>341</v>
+      </c>
     </row>
-    <row r="12" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A12" s="43" t="s">
+    <row r="13" spans="1:18" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A13" s="43" t="s">
         <v>414</v>
       </c>
-      <c r="B12" s="73" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="74"/>
-      <c r="D12" s="44" t="s">
+      <c r="B13" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="70"/>
+      <c r="D13" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E13" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F13" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G13" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H13" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="I12" s="44" t="s">
+      <c r="I13" s="44" t="s">
         <v>190</v>
       </c>
-      <c r="J12" s="44" t="s">
+      <c r="J13" s="44" t="s">
         <v>214</v>
       </c>
-      <c r="K12" s="44" t="s">
+      <c r="K13" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="L12" s="44" t="s">
+      <c r="L13" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="M12" s="44" t="s">
+      <c r="M13" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="N12" s="44" t="s">
+      <c r="N13" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="O12" s="44" t="s">
-        <v>340</v>
-      </c>
-      <c r="P12" s="44" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q12" s="44" t="s">
+      <c r="O13" s="44" t="s">
         <v>342</v>
       </c>
+      <c r="P13" s="44" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q13" s="44" t="s">
+        <v>344</v>
+      </c>
     </row>
-    <row r="13" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A13" s="43" t="s">
+    <row r="14" spans="1:18" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A14" s="43" t="s">
         <v>415</v>
       </c>
-      <c r="B13" s="73" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="44" t="s">
+      <c r="B14" s="69" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="70"/>
+      <c r="D14" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E14" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F14" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="G13" s="44" t="s">
+      <c r="G14" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H14" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I14" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="J13" s="44" t="s">
+      <c r="J14" s="44" t="s">
         <v>215</v>
       </c>
-      <c r="K13" s="44" t="s">
+      <c r="K14" s="44" t="s">
         <v>239</v>
       </c>
-      <c r="L13" s="44" t="s">
+      <c r="L14" s="44" t="s">
         <v>263</v>
       </c>
-      <c r="M13" s="44" t="s">
+      <c r="M14" s="44" t="s">
         <v>287</v>
       </c>
-      <c r="N13" s="44" t="s">
+      <c r="N14" s="44" t="s">
         <v>311</v>
       </c>
-      <c r="O13" s="44" t="s">
-        <v>343</v>
-      </c>
-      <c r="P13" s="44" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q13" s="44" t="s">
+      <c r="O14" s="44" t="s">
         <v>345</v>
       </c>
+      <c r="P14" s="44" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q14" s="44" t="s">
+        <v>347</v>
+      </c>
     </row>
-    <row r="14" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A14" s="43" t="s">
+    <row r="15" spans="1:18" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A15" s="43" t="s">
         <v>416</v>
       </c>
-      <c r="B14" s="73" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="74"/>
-      <c r="D14" s="44" t="s">
+      <c r="B15" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="70"/>
+      <c r="D15" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="44" t="s">
+      <c r="E15" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="F14" s="44" t="s">
+      <c r="F15" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G15" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H15" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="I14" s="44" t="s">
+      <c r="I15" s="44" t="s">
         <v>192</v>
       </c>
-      <c r="J14" s="44" t="s">
+      <c r="J15" s="44" t="s">
         <v>216</v>
       </c>
-      <c r="K14" s="44" t="s">
+      <c r="K15" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="L14" s="44" t="s">
+      <c r="L15" s="44" t="s">
         <v>264</v>
       </c>
-      <c r="M14" s="44" t="s">
+      <c r="M15" s="44" t="s">
         <v>288</v>
       </c>
-      <c r="N14" s="44" t="s">
+      <c r="N15" s="44" t="s">
         <v>312</v>
       </c>
-      <c r="O14" s="44" t="s">
-        <v>346</v>
-      </c>
-      <c r="P14" s="44" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q14" s="44" t="s">
+      <c r="O15" s="44" t="s">
         <v>348</v>
       </c>
+      <c r="P15" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q15" s="44" t="s">
+        <v>350</v>
+      </c>
     </row>
-    <row r="15" spans="1:18" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A15" s="43" t="s">
+    <row r="16" spans="1:18" s="26" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A16" s="43" t="s">
         <v>417</v>
       </c>
-      <c r="B15" s="73" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="74"/>
-      <c r="D15" s="44" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="G15" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="H15" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="I15" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="J15" s="44" t="s">
-        <v>217</v>
-      </c>
-      <c r="K15" s="44" t="s">
-        <v>241</v>
-      </c>
-      <c r="L15" s="44" t="s">
-        <v>265</v>
-      </c>
-      <c r="M15" s="44" t="s">
-        <v>289</v>
-      </c>
-      <c r="N15" s="44" t="s">
-        <v>313</v>
-      </c>
-      <c r="O15" s="44" t="s">
-        <v>349</v>
-      </c>
-      <c r="P15" s="44" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q15" s="44" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" s="26" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A16" s="43" t="s">
-        <v>418</v>
-      </c>
-      <c r="B16" s="77" t="s">
+      <c r="B16" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="78"/>
+      <c r="C16" s="76"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -3063,218 +3065,218 @@
       <c r="P16" s="22"/>
       <c r="Q16" s="25"/>
     </row>
-    <row r="17" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
+    <row r="17" spans="1:17" s="24" customFormat="1" ht="15.9" customHeight="1">
       <c r="A17" s="43" t="s">
+        <v>418</v>
+      </c>
+      <c r="B17" s="69" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="I17" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="J17" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="K17" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="L17" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="M17" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="N17" s="44" t="s">
+        <v>313</v>
+      </c>
+      <c r="O17" s="44" t="s">
+        <v>351</v>
+      </c>
+      <c r="P17" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q17" s="44" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A18" s="43" t="s">
         <v>419</v>
       </c>
-      <c r="B17" s="73" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="74"/>
-      <c r="D17" s="44" t="s">
+      <c r="B18" s="69" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="44" t="s">
+      <c r="E18" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="F17" s="44" t="s">
+      <c r="F18" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="G17" s="44" t="s">
+      <c r="G18" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H18" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="I17" s="44" t="s">
+      <c r="I18" s="44" t="s">
         <v>194</v>
       </c>
-      <c r="J17" s="44" t="s">
+      <c r="J18" s="44" t="s">
         <v>218</v>
       </c>
-      <c r="K17" s="44" t="s">
+      <c r="K18" s="44" t="s">
         <v>242</v>
       </c>
-      <c r="L17" s="44" t="s">
+      <c r="L18" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="M17" s="44" t="s">
+      <c r="M18" s="44" t="s">
         <v>290</v>
       </c>
-      <c r="N17" s="44" t="s">
+      <c r="N18" s="44" t="s">
         <v>314</v>
       </c>
-      <c r="O17" s="44" t="s">
-        <v>352</v>
-      </c>
-      <c r="P17" s="44" t="s">
-        <v>353</v>
-      </c>
-      <c r="Q17" s="44" t="s">
+      <c r="O18" s="44" t="s">
         <v>354</v>
       </c>
+      <c r="P18" s="44" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q18" s="44" t="s">
+        <v>356</v>
+      </c>
     </row>
-    <row r="18" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A18" s="43" t="s">
+    <row r="19" spans="1:17" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A19" s="43" t="s">
         <v>420</v>
       </c>
-      <c r="B18" s="73" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="74"/>
-      <c r="D18" s="44" t="s">
+      <c r="B19" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="70"/>
+      <c r="D19" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="44" t="s">
+      <c r="E19" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="F18" s="44" t="s">
+      <c r="F19" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="G18" s="44" t="s">
+      <c r="G19" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H19" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I19" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="J18" s="44" t="s">
+      <c r="J19" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="K18" s="44" t="s">
+      <c r="K19" s="44" t="s">
         <v>243</v>
       </c>
-      <c r="L18" s="44" t="s">
+      <c r="L19" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="M18" s="44" t="s">
+      <c r="M19" s="44" t="s">
         <v>291</v>
       </c>
-      <c r="N18" s="44" t="s">
+      <c r="N19" s="44" t="s">
         <v>315</v>
       </c>
-      <c r="O18" s="44" t="s">
-        <v>355</v>
-      </c>
-      <c r="P18" s="44" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q18" s="44" t="s">
+      <c r="O19" s="44" t="s">
         <v>357</v>
       </c>
+      <c r="P19" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q19" s="44" t="s">
+        <v>359</v>
+      </c>
     </row>
-    <row r="19" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A19" s="43" t="s">
+    <row r="20" spans="1:17" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A20" s="43" t="s">
         <v>421</v>
       </c>
-      <c r="B19" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="74"/>
-      <c r="D19" s="44" t="s">
+      <c r="B20" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="70"/>
+      <c r="D20" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="E20" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="44" t="s">
+      <c r="F20" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="G19" s="44" t="s">
+      <c r="G20" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H20" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="I19" s="44" t="s">
+      <c r="I20" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="J19" s="44" t="s">
+      <c r="J20" s="44" t="s">
         <v>220</v>
       </c>
-      <c r="K19" s="44" t="s">
+      <c r="K20" s="44" t="s">
         <v>244</v>
       </c>
-      <c r="L19" s="44" t="s">
+      <c r="L20" s="44" t="s">
         <v>268</v>
       </c>
-      <c r="M19" s="44" t="s">
+      <c r="M20" s="44" t="s">
         <v>292</v>
       </c>
-      <c r="N19" s="44" t="s">
+      <c r="N20" s="44" t="s">
         <v>316</v>
       </c>
-      <c r="O19" s="44" t="s">
-        <v>358</v>
-      </c>
-      <c r="P19" s="44" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q19" s="44" t="s">
+      <c r="O20" s="44" t="s">
         <v>360</v>
       </c>
+      <c r="P20" s="44" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q20" s="44" t="s">
+        <v>362</v>
+      </c>
     </row>
-    <row r="20" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A20" s="43" t="s">
+    <row r="21" spans="1:17" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A21" s="43" t="s">
         <v>422</v>
       </c>
-      <c r="B20" s="73" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="74"/>
-      <c r="D20" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="44" t="s">
-        <v>101</v>
-      </c>
-      <c r="F20" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="G20" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="H20" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="I20" s="44" t="s">
-        <v>197</v>
-      </c>
-      <c r="J20" s="44" t="s">
-        <v>221</v>
-      </c>
-      <c r="K20" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="L20" s="44" t="s">
-        <v>269</v>
-      </c>
-      <c r="M20" s="44" t="s">
-        <v>293</v>
-      </c>
-      <c r="N20" s="44" t="s">
-        <v>317</v>
-      </c>
-      <c r="O20" s="44" t="s">
-        <v>361</v>
-      </c>
-      <c r="P20" s="44" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q20" s="44" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A21" s="43" t="s">
-        <v>423</v>
-      </c>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="76"/>
+      <c r="C21" s="68"/>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
@@ -3290,116 +3292,116 @@
       <c r="P21" s="22"/>
       <c r="Q21" s="25"/>
     </row>
-    <row r="22" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
+    <row r="22" spans="1:17" s="24" customFormat="1" ht="15.9" customHeight="1">
       <c r="A22" s="43" t="s">
+        <v>423</v>
+      </c>
+      <c r="B22" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="H22" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="I22" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="J22" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="K22" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="L22" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="M22" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="N22" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="O22" s="44" t="s">
+        <v>363</v>
+      </c>
+      <c r="P22" s="44" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q22" s="44" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A23" s="43" t="s">
         <v>424</v>
       </c>
-      <c r="B22" s="73" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="74"/>
-      <c r="D22" s="44" t="s">
+      <c r="B23" s="69" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="70"/>
+      <c r="D23" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="E22" s="44" t="s">
+      <c r="E23" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="F22" s="44" t="s">
+      <c r="F23" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="G22" s="44" t="s">
+      <c r="G23" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H23" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="I22" s="44" t="s">
+      <c r="I23" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="J22" s="44" t="s">
+      <c r="J23" s="44" t="s">
         <v>222</v>
       </c>
-      <c r="K22" s="44" t="s">
+      <c r="K23" s="44" t="s">
         <v>246</v>
       </c>
-      <c r="L22" s="44" t="s">
+      <c r="L23" s="44" t="s">
         <v>270</v>
       </c>
-      <c r="M22" s="44" t="s">
+      <c r="M23" s="44" t="s">
         <v>294</v>
       </c>
-      <c r="N22" s="44" t="s">
+      <c r="N23" s="44" t="s">
         <v>318</v>
       </c>
-      <c r="O22" s="44" t="s">
-        <v>364</v>
-      </c>
-      <c r="P22" s="44" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q22" s="44" t="s">
+      <c r="O23" s="44" t="s">
         <v>366</v>
       </c>
+      <c r="P23" s="44" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q23" s="44" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="23" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A23" s="43" t="s">
+    <row r="24" spans="1:17" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A24" s="43" t="s">
         <v>425</v>
       </c>
-      <c r="B23" s="73" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="74"/>
-      <c r="D23" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>151</v>
-      </c>
-      <c r="H23" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="I23" s="44" t="s">
-        <v>199</v>
-      </c>
-      <c r="J23" s="44" t="s">
-        <v>223</v>
-      </c>
-      <c r="K23" s="44" t="s">
-        <v>247</v>
-      </c>
-      <c r="L23" s="44" t="s">
-        <v>271</v>
-      </c>
-      <c r="M23" s="44" t="s">
-        <v>295</v>
-      </c>
-      <c r="N23" s="44" t="s">
-        <v>319</v>
-      </c>
-      <c r="O23" s="44" t="s">
-        <v>367</v>
-      </c>
-      <c r="P23" s="44" t="s">
-        <v>368</v>
-      </c>
-      <c r="Q23" s="44" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A24" s="43" t="s">
-        <v>426</v>
-      </c>
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="81"/>
+      <c r="C24" s="72"/>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -3415,116 +3417,116 @@
       <c r="P24" s="22"/>
       <c r="Q24" s="25"/>
     </row>
-    <row r="25" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
+    <row r="25" spans="1:17" s="24" customFormat="1" ht="15.9" customHeight="1">
       <c r="A25" s="43" t="s">
+        <v>426</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="58"/>
+      <c r="D25" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="H25" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="J25" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="K25" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="L25" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="M25" s="44" t="s">
+        <v>295</v>
+      </c>
+      <c r="N25" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="O25" s="44" t="s">
+        <v>369</v>
+      </c>
+      <c r="P25" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q25" s="44" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="24" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A26" s="43" t="s">
         <v>427</v>
       </c>
-      <c r="B25" s="82" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="79"/>
-      <c r="D25" s="44" t="s">
+      <c r="B26" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="58"/>
+      <c r="D26" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="E26" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="44" t="s">
+      <c r="F26" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="G25" s="44" t="s">
+      <c r="G26" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H26" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="I25" s="44" t="s">
+      <c r="I26" s="44" t="s">
         <v>200</v>
       </c>
-      <c r="J25" s="44" t="s">
+      <c r="J26" s="44" t="s">
         <v>224</v>
       </c>
-      <c r="K25" s="44" t="s">
+      <c r="K26" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="L25" s="44" t="s">
+      <c r="L26" s="44" t="s">
         <v>272</v>
       </c>
-      <c r="M25" s="44" t="s">
+      <c r="M26" s="44" t="s">
         <v>296</v>
       </c>
-      <c r="N25" s="44" t="s">
+      <c r="N26" s="44" t="s">
         <v>320</v>
       </c>
-      <c r="O25" s="44" t="s">
-        <v>370</v>
-      </c>
-      <c r="P25" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="Q25" s="44" t="s">
+      <c r="O26" s="44" t="s">
         <v>372</v>
       </c>
+      <c r="P26" s="44" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q26" s="44" t="s">
+        <v>374</v>
+      </c>
     </row>
-    <row r="26" spans="1:17" s="24" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A26" s="43" t="s">
+    <row r="27" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A27" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="B26" s="82" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="79"/>
-      <c r="D26" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="F26" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="G26" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="H26" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="I26" s="44" t="s">
-        <v>201</v>
-      </c>
-      <c r="J26" s="44" t="s">
-        <v>225</v>
-      </c>
-      <c r="K26" s="44" t="s">
-        <v>249</v>
-      </c>
-      <c r="L26" s="44" t="s">
-        <v>273</v>
-      </c>
-      <c r="M26" s="44" t="s">
-        <v>297</v>
-      </c>
-      <c r="N26" s="44" t="s">
-        <v>321</v>
-      </c>
-      <c r="O26" s="44" t="s">
-        <v>373</v>
-      </c>
-      <c r="P26" s="44" t="s">
-        <v>374</v>
-      </c>
-      <c r="Q26" s="44" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A27" s="43" t="s">
-        <v>429</v>
-      </c>
-      <c r="B27" s="80" t="s">
+      <c r="B27" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="81"/>
+      <c r="C27" s="72"/>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
@@ -3540,116 +3542,116 @@
       <c r="P27" s="22"/>
       <c r="Q27" s="25"/>
     </row>
-    <row r="28" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
+    <row r="28" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1">
       <c r="A28" s="43" t="s">
+        <v>429</v>
+      </c>
+      <c r="B28" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="58"/>
+      <c r="D28" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>153</v>
+      </c>
+      <c r="H28" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="I28" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="J28" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="K28" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="L28" s="44" t="s">
+        <v>273</v>
+      </c>
+      <c r="M28" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="N28" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="O28" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="P28" s="44" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q28" s="44" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A29" s="43" t="s">
         <v>430</v>
       </c>
-      <c r="B28" s="82" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="79"/>
-      <c r="D28" s="44" t="s">
+      <c r="B29" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="74"/>
+      <c r="D29" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="E28" s="44" t="s">
+      <c r="E29" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="F28" s="44" t="s">
+      <c r="F29" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="G28" s="44" t="s">
+      <c r="G29" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="H28" s="44" t="s">
+      <c r="H29" s="44" t="s">
         <v>178</v>
       </c>
-      <c r="I28" s="44" t="s">
+      <c r="I29" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="J28" s="44" t="s">
-        <v>226</v>
-      </c>
-      <c r="K28" s="44" t="s">
+      <c r="J29" s="44" t="s">
+        <v>233</v>
+      </c>
+      <c r="K29" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="L28" s="44" t="s">
+      <c r="L29" s="44" t="s">
         <v>274</v>
       </c>
-      <c r="M28" s="44" t="s">
+      <c r="M29" s="44" t="s">
         <v>298</v>
       </c>
-      <c r="N28" s="44" t="s">
+      <c r="N29" s="44" t="s">
         <v>322</v>
       </c>
-      <c r="O28" s="44" t="s">
-        <v>376</v>
-      </c>
-      <c r="P28" s="44" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q28" s="44" t="s">
+      <c r="O29" s="44" t="s">
         <v>378</v>
       </c>
+      <c r="P29" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q29" s="44" t="s">
+        <v>380</v>
+      </c>
     </row>
-    <row r="29" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A29" s="43" t="s">
-        <v>431</v>
-      </c>
-      <c r="B29" s="83" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="84"/>
-      <c r="D29" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="E29" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="F29" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="G29" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="H29" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="I29" s="44" t="s">
-        <v>203</v>
-      </c>
-      <c r="J29" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="K29" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="L29" s="44" t="s">
-        <v>275</v>
-      </c>
-      <c r="M29" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="N29" s="44" t="s">
-        <v>323</v>
-      </c>
-      <c r="O29" s="44" t="s">
-        <v>379</v>
-      </c>
-      <c r="P29" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q29" s="44" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
+    <row r="30" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1">
       <c r="A30" s="20" t="s">
-        <v>440</v>
-      </c>
-      <c r="B30" s="79" t="s">
+        <v>439</v>
+      </c>
+      <c r="B30" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="79"/>
+      <c r="C30" s="58"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -3665,218 +3667,218 @@
       <c r="P30" s="22"/>
       <c r="Q30" s="25"/>
     </row>
-    <row r="31" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
+    <row r="31" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1">
       <c r="A31" s="43" t="s">
-        <v>432</v>
-      </c>
-      <c r="B31" s="79" t="s">
+        <v>431</v>
+      </c>
+      <c r="B31" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="79"/>
+      <c r="C31" s="58"/>
       <c r="D31" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="F31" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="H31" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="I31" s="44" t="s">
+        <v>203</v>
+      </c>
+      <c r="J31" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="K31" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="L31" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="M31" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="N31" s="44" t="s">
+        <v>323</v>
+      </c>
+      <c r="O31" s="44" t="s">
+        <v>381</v>
+      </c>
+      <c r="P31" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q31" s="44" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A32" s="20" t="s">
+        <v>433</v>
+      </c>
+      <c r="B32" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="58"/>
+      <c r="D32" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="E32" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="F31" s="44" t="s">
+      <c r="F32" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="G31" s="44" t="s">
+      <c r="G32" s="44" t="s">
         <v>156</v>
       </c>
-      <c r="H31" s="44" t="s">
+      <c r="H32" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="I31" s="44" t="s">
+      <c r="I32" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="J31" s="44" t="s">
+      <c r="J32" s="44" t="s">
         <v>227</v>
       </c>
-      <c r="K31" s="44" t="s">
+      <c r="K32" s="44" t="s">
         <v>252</v>
       </c>
-      <c r="L31" s="44" t="s">
+      <c r="L32" s="44" t="s">
         <v>276</v>
       </c>
-      <c r="M31" s="44" t="s">
+      <c r="M32" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="N31" s="44" t="s">
+      <c r="N32" s="44" t="s">
         <v>324</v>
       </c>
-      <c r="O31" s="44" t="s">
-        <v>382</v>
-      </c>
-      <c r="P31" s="44" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q31" s="44" t="s">
+      <c r="O32" s="44" t="s">
         <v>384</v>
       </c>
+      <c r="P32" s="44" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q32" s="44" t="s">
+        <v>386</v>
+      </c>
     </row>
-    <row r="32" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A32" s="20" t="s">
-        <v>434</v>
-      </c>
-      <c r="B32" s="79" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="79"/>
-      <c r="D32" s="44" t="s">
+    <row r="33" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A33" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="B33" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="58"/>
+      <c r="D33" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="E32" s="44" t="s">
+      <c r="E33" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="F32" s="44" t="s">
+      <c r="F33" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="G32" s="44" t="s">
+      <c r="G33" s="44" t="s">
         <v>157</v>
       </c>
-      <c r="H32" s="44" t="s">
+      <c r="H33" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="I32" s="44" t="s">
+      <c r="I33" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="J32" s="44" t="s">
+      <c r="J33" s="44" t="s">
         <v>228</v>
       </c>
-      <c r="K32" s="44" t="s">
+      <c r="K33" s="44" t="s">
         <v>253</v>
       </c>
-      <c r="L32" s="44" t="s">
+      <c r="L33" s="44" t="s">
         <v>277</v>
       </c>
-      <c r="M32" s="44" t="s">
+      <c r="M33" s="44" t="s">
         <v>301</v>
       </c>
-      <c r="N32" s="44" t="s">
+      <c r="N33" s="44" t="s">
         <v>325</v>
       </c>
-      <c r="O32" s="44" t="s">
-        <v>385</v>
-      </c>
-      <c r="P32" s="44" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q32" s="44" t="s">
+      <c r="O33" s="44" t="s">
         <v>387</v>
       </c>
+      <c r="P33" s="44" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q33" s="44" t="s">
+        <v>389</v>
+      </c>
     </row>
-    <row r="33" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A33" s="20" t="s">
-        <v>439</v>
-      </c>
-      <c r="B33" s="79" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="79"/>
-      <c r="D33" s="44" t="s">
+    <row r="34" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1" thickBot="1">
+      <c r="A34" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B34" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="60"/>
+      <c r="D34" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="44" t="s">
+      <c r="E34" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="F33" s="44" t="s">
+      <c r="F34" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="G33" s="44" t="s">
+      <c r="G34" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="H33" s="44" t="s">
+      <c r="H34" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="I33" s="44" t="s">
+      <c r="I34" s="44" t="s">
         <v>206</v>
       </c>
-      <c r="J33" s="44" t="s">
+      <c r="J34" s="44" t="s">
         <v>229</v>
       </c>
-      <c r="K33" s="44" t="s">
+      <c r="K34" s="44" t="s">
         <v>254</v>
       </c>
-      <c r="L33" s="44" t="s">
+      <c r="L34" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="M33" s="44" t="s">
+      <c r="M34" s="44" t="s">
         <v>302</v>
       </c>
-      <c r="N33" s="44" t="s">
+      <c r="N34" s="44" t="s">
         <v>326</v>
       </c>
-      <c r="O33" s="44" t="s">
-        <v>388</v>
-      </c>
-      <c r="P33" s="44" t="s">
-        <v>389</v>
-      </c>
-      <c r="Q33" s="44" t="s">
+      <c r="O34" s="44" t="s">
         <v>390</v>
       </c>
+      <c r="P34" s="44" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q34" s="44" t="s">
+        <v>392</v>
+      </c>
     </row>
-    <row r="34" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1" thickBot="1">
-      <c r="A34" s="20" t="s">
+    <row r="35" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
+      <c r="A35" s="20" t="s">
         <v>437</v>
       </c>
-      <c r="B34" s="86" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="87"/>
-      <c r="D34" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="E34" s="44" t="s">
-        <v>111</v>
-      </c>
-      <c r="F34" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="G34" s="44" t="s">
-        <v>159</v>
-      </c>
-      <c r="H34" s="44" t="s">
-        <v>183</v>
-      </c>
-      <c r="I34" s="44" t="s">
-        <v>207</v>
-      </c>
-      <c r="J34" s="44" t="s">
-        <v>230</v>
-      </c>
-      <c r="K34" s="44" t="s">
-        <v>255</v>
-      </c>
-      <c r="L34" s="44" t="s">
-        <v>279</v>
-      </c>
-      <c r="M34" s="44" t="s">
-        <v>303</v>
-      </c>
-      <c r="N34" s="44" t="s">
-        <v>327</v>
-      </c>
-      <c r="O34" s="44" t="s">
-        <v>391</v>
-      </c>
-      <c r="P34" s="44" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q34" s="44" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1" thickTop="1">
-      <c r="A35" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="B35" s="88" t="s">
+      <c r="B35" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="89"/>
+      <c r="C35" s="62"/>
       <c r="D35" s="27"/>
       <c r="E35" s="28"/>
       <c r="F35" s="29"/>
@@ -3892,196 +3894,196 @@
       <c r="P35" s="29"/>
       <c r="Q35" s="30"/>
     </row>
-    <row r="36" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
+    <row r="36" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1">
       <c r="A36" s="20" t="s">
-        <v>436</v>
-      </c>
-      <c r="B36" s="82" t="s">
+        <v>435</v>
+      </c>
+      <c r="B36" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="79"/>
+      <c r="C36" s="58"/>
       <c r="D36" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="H36" s="44" t="s">
+        <v>183</v>
+      </c>
+      <c r="I36" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="J36" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="K36" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="L36" s="44" t="s">
+        <v>279</v>
+      </c>
+      <c r="M36" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="N36" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="O36" s="44" t="s">
+        <v>393</v>
+      </c>
+      <c r="P36" s="44" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q36" s="44" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1">
+      <c r="A37" s="43" t="s">
+        <v>432</v>
+      </c>
+      <c r="B37" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="63"/>
+      <c r="D37" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E37" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="F36" s="44" t="s">
+      <c r="F37" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="G36" s="44" t="s">
+      <c r="G37" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="H36" s="44" t="s">
+      <c r="H37" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="I36" s="44" t="s">
+      <c r="I37" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="J36" s="44" t="s">
+      <c r="J37" s="44" t="s">
         <v>231</v>
       </c>
-      <c r="K36" s="44" t="s">
+      <c r="K37" s="44" t="s">
         <v>256</v>
       </c>
-      <c r="L36" s="44" t="s">
+      <c r="L37" s="44" t="s">
         <v>280</v>
       </c>
-      <c r="M36" s="44" t="s">
+      <c r="M37" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="N36" s="44" t="s">
+      <c r="N37" s="44" t="s">
         <v>328</v>
       </c>
-      <c r="O36" s="44" t="s">
-        <v>394</v>
-      </c>
-      <c r="P36" s="44" t="s">
-        <v>395</v>
-      </c>
-      <c r="Q36" s="44" t="s">
+      <c r="O37" s="44" t="s">
         <v>396</v>
       </c>
+      <c r="P37" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q37" s="44" t="s">
+        <v>398</v>
+      </c>
     </row>
-    <row r="37" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A37" s="43" t="s">
-        <v>433</v>
-      </c>
-      <c r="B37" s="90" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="82"/>
-      <c r="D37" s="44" t="s">
+    <row r="38" spans="1:17" s="11" customFormat="1" ht="15.9" customHeight="1" thickBot="1">
+      <c r="A38" s="20" t="s">
+        <v>434</v>
+      </c>
+      <c r="B38" s="65" t="s">
+        <v>442</v>
+      </c>
+      <c r="C38" s="66"/>
+      <c r="D38" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="E37" s="44" t="s">
+      <c r="E38" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="F37" s="44" t="s">
+      <c r="F38" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="G37" s="44" t="s">
+      <c r="G38" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="H37" s="44" t="s">
+      <c r="H38" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="I37" s="44" t="s">
+      <c r="I38" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="J37" s="44" t="s">
+      <c r="J38" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="K37" s="44" t="s">
+      <c r="K38" s="44" t="s">
         <v>257</v>
       </c>
-      <c r="L37" s="44" t="s">
+      <c r="L38" s="44" t="s">
         <v>281</v>
       </c>
-      <c r="M37" s="44" t="s">
+      <c r="M38" s="44" t="s">
         <v>305</v>
       </c>
-      <c r="N37" s="44" t="s">
+      <c r="N38" s="44" t="s">
         <v>329</v>
       </c>
-      <c r="O37" s="44" t="s">
-        <v>397</v>
-      </c>
-      <c r="P37" s="44" t="s">
-        <v>398</v>
-      </c>
-      <c r="Q37" s="44" t="s">
+      <c r="O38" s="44" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" s="11" customFormat="1" ht="15.95" customHeight="1" thickBot="1">
-      <c r="A38" s="20" t="s">
-        <v>435</v>
-      </c>
-      <c r="B38" s="91" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" s="92"/>
-      <c r="D38" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="F38" s="44" t="s">
-        <v>138</v>
-      </c>
-      <c r="G38" s="44" t="s">
-        <v>162</v>
-      </c>
-      <c r="H38" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="I38" s="44" t="s">
-        <v>210</v>
-      </c>
-      <c r="J38" s="44" t="s">
-        <v>233</v>
-      </c>
-      <c r="K38" s="44" t="s">
-        <v>258</v>
-      </c>
-      <c r="L38" s="44" t="s">
-        <v>282</v>
-      </c>
-      <c r="M38" s="44" t="s">
-        <v>306</v>
-      </c>
-      <c r="N38" s="44" t="s">
-        <v>330</v>
-      </c>
-      <c r="O38" s="44" t="s">
+      <c r="P38" s="44" t="s">
         <v>400</v>
       </c>
-      <c r="P38" s="44" t="s">
+      <c r="Q38" s="44" t="s">
         <v>401</v>
-      </c>
-      <c r="Q38" s="44" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="11" customFormat="1" ht="48.75" customHeight="1">
-      <c r="A39" s="85" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" s="85"/>
-      <c r="C39" s="85"/>
-      <c r="D39" s="85"/>
-      <c r="E39" s="85"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="85"/>
-      <c r="H39" s="85"/>
-      <c r="I39" s="85"/>
-      <c r="J39" s="85"/>
-      <c r="K39" s="85"/>
-      <c r="L39" s="85"/>
-      <c r="M39" s="85"/>
-      <c r="N39" s="85"/>
-      <c r="O39" s="85"/>
-      <c r="P39" s="85"/>
-      <c r="Q39" s="85"/>
+      <c r="A39" s="57" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="57"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
     </row>
     <row r="40" spans="1:17" s="33" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A40" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B40" s="31" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C40" s="31"/>
       <c r="D40" s="31"/>
       <c r="E40" s="32"/>
       <c r="F40" s="31"/>
       <c r="G40" s="33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H40" s="34" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I40" s="34"/>
       <c r="J40" s="34"/>
@@ -4091,10 +4093,10 @@
       <c r="N40" s="37"/>
       <c r="O40" s="31"/>
       <c r="P40" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q40" s="38" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="14.25" customHeight="1">
@@ -4103,13 +4105,30 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A39:Q39"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
@@ -4122,38 +4141,21 @@
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="A39:Q39"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:E4"/>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B4:C4">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:E4" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B4:C4" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"--,01-银行非保本理财,02-信托公司资管产品,03-证券公司及其子公司资管产品,04-基金管理公司及其子公司专户,05-期货公司及其子公司资管产品,06-保险资管产品,07-金融资产投资公司资管产品,08-公募基金"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$L$8:$L$17</formula1>
     </dataValidation>
   </dataValidations>
